--- a/results/supplementary_data.xlsx
+++ b/results/supplementary_data.xlsx
@@ -7552,7 +7552,7 @@
     </x:row>
     <x:row r="28">
       <x:c r="A28" s="38" t="str">
-        <x:v>TGF¦Â1</x:v>
+        <x:v>TGF-beta1</x:v>
       </x:c>
       <x:c r="B28" s="47" t="n">
         <x:v>3</x:v>
